--- a/docs/PRJ301_SE20C_GROUP4.xlsx
+++ b/docs/PRJ301_SE20C_GROUP4.xlsx
@@ -4,14 +4,15 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="21876" windowHeight="9840" activeTab="3"/>
+    <workbookView windowWidth="21876" windowHeight="9840" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="0.Overview" sheetId="1" r:id="rId1"/>
     <sheet name="1. Week 1" sheetId="2" r:id="rId2"/>
     <sheet name="1. Week 2" sheetId="5" r:id="rId3"/>
     <sheet name="Week 4" sheetId="3" r:id="rId4"/>
-    <sheet name="Instruction" sheetId="4" r:id="rId5"/>
+    <sheet name="Week 5" sheetId="7" r:id="rId5"/>
+    <sheet name="Instruction" sheetId="4" r:id="rId6"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -31,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="196" uniqueCount="148">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="206" uniqueCount="148">
   <si>
     <t>PRJ301 - Project AI Usage Report</t>
   </si>
@@ -940,7 +941,7 @@
     <font>
       <u/>
       <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <color rgb="FF800080"/>
       <name val="Calibri"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -954,7 +955,7 @@
     <font>
       <u/>
       <sz val="11"/>
-      <color rgb="FF800080"/>
+      <color rgb="FF0000FF"/>
       <name val="Calibri"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -1497,7 +1498,7 @@
     <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1627,7 +1628,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1653,12 +1654,15 @@
     <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="6" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="6" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1668,7 +1672,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="6" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="6" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1683,7 +1687,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="6" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="6" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -1692,10 +1696,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="6" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="6" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="6" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="6" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2066,74 +2070,74 @@
   </cols>
   <sheetData>
     <row r="1" ht="28.05" customHeight="1" spans="1:5">
-      <c r="A1" s="24" t="s">
+      <c r="A1" s="25" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:5">
-      <c r="A3" s="25" t="s">
+      <c r="A3" s="26" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="26" t="s">
+      <c r="B3" s="27" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:5">
-      <c r="A4" s="25" t="s">
+      <c r="A4" s="26" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="26" t="s">
+      <c r="B4" s="27" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="5" spans="1:5">
-      <c r="A5" s="25" t="s">
+      <c r="A5" s="26" t="s">
         <v>5</v>
       </c>
-      <c r="B5" s="26" t="s">
+      <c r="B5" s="27" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="6" spans="1:5">
-      <c r="A6" s="25" t="s">
+      <c r="A6" s="26" t="s">
         <v>7</v>
       </c>
-      <c r="B6" s="26" t="s">
+      <c r="B6" s="27" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="7" spans="1:5">
-      <c r="A7" s="25" t="s">
+      <c r="A7" s="26" t="s">
         <v>9</v>
       </c>
-      <c r="B7" s="26" t="s">
+      <c r="B7" s="27" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="8" spans="1:5">
-      <c r="A8" s="25" t="s">
+      <c r="A8" s="26" t="s">
         <v>11</v>
       </c>
-      <c r="B8" s="26">
+      <c r="B8" s="27">
         <v>4</v>
       </c>
     </row>
     <row r="9" spans="1:5">
-      <c r="A9" s="25" t="s">
+      <c r="A9" s="26" t="s">
         <v>12</v>
       </c>
-      <c r="B9" s="26" t="s">
+      <c r="B9" s="27" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="11" spans="1:5">
-      <c r="A11" s="25" t="s">
+      <c r="A11" s="26" t="s">
         <v>14</v>
       </c>
-      <c r="B11" s="27"/>
-      <c r="C11" s="27"/>
-      <c r="D11" s="27"/>
-      <c r="E11" s="28"/>
+      <c r="B11" s="28"/>
+      <c r="C11" s="28"/>
+      <c r="D11" s="28"/>
+      <c r="E11" s="29"/>
     </row>
     <row r="12" spans="1:5">
       <c r="A12" s="4" t="s">
@@ -2153,87 +2157,87 @@
       </c>
     </row>
     <row r="13" spans="1:5">
-      <c r="A13" s="29">
+      <c r="A13" s="30">
         <v>1</v>
       </c>
-      <c r="B13" s="26" t="s">
+      <c r="B13" s="27" t="s">
         <v>20</v>
       </c>
-      <c r="C13" s="26" t="s">
+      <c r="C13" s="27" t="s">
         <v>21</v>
       </c>
-      <c r="D13" s="26" t="s">
+      <c r="D13" s="27" t="s">
         <v>22</v>
       </c>
-      <c r="E13" s="26" t="s">
+      <c r="E13" s="27" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="14" spans="1:5">
-      <c r="A14" s="29">
+      <c r="A14" s="30">
         <v>2</v>
       </c>
-      <c r="B14" s="26" t="s">
+      <c r="B14" s="27" t="s">
         <v>24</v>
       </c>
-      <c r="C14" s="26" t="s">
+      <c r="C14" s="27" t="s">
         <v>25</v>
       </c>
-      <c r="D14" s="26" t="s">
+      <c r="D14" s="27" t="s">
         <v>22</v>
       </c>
-      <c r="E14" s="26" t="s">
+      <c r="E14" s="27" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="15" ht="26.4" spans="1:5">
-      <c r="A15" s="29">
+      <c r="A15" s="30">
         <v>3</v>
       </c>
-      <c r="B15" s="26" t="s">
+      <c r="B15" s="27" t="s">
         <v>27</v>
       </c>
-      <c r="C15" s="26" t="s">
+      <c r="C15" s="27" t="s">
         <v>28</v>
       </c>
-      <c r="D15" s="26" t="s">
+      <c r="D15" s="27" t="s">
         <v>29</v>
       </c>
-      <c r="E15" s="26" t="s">
+      <c r="E15" s="27" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="16" spans="1:5">
-      <c r="A16" s="29">
+      <c r="A16" s="30">
         <v>4</v>
       </c>
-      <c r="B16" s="26" t="s">
+      <c r="B16" s="27" t="s">
         <v>31</v>
       </c>
-      <c r="C16" s="26" t="s">
+      <c r="C16" s="27" t="s">
         <v>32</v>
       </c>
-      <c r="D16" s="26" t="s">
+      <c r="D16" s="27" t="s">
         <v>22</v>
       </c>
-      <c r="E16" s="26" t="s">
+      <c r="E16" s="27" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="17" spans="1:5">
-      <c r="A17" s="29">
+      <c r="A17" s="30">
         <v>5</v>
       </c>
-      <c r="B17" s="26" t="s">
+      <c r="B17" s="27" t="s">
         <v>34</v>
       </c>
-      <c r="C17" s="26" t="s">
+      <c r="C17" s="27" t="s">
         <v>35</v>
       </c>
-      <c r="D17" s="26" t="s">
+      <c r="D17" s="27" t="s">
         <v>22</v>
       </c>
-      <c r="E17" s="26" t="s">
+      <c r="E17" s="27" t="s">
         <v>33</v>
       </c>
     </row>
@@ -2305,98 +2309,98 @@
       </c>
     </row>
     <row r="2" ht="96" customHeight="1" spans="1:10">
-      <c r="A2" s="11">
+      <c r="A2" s="12">
         <v>1</v>
       </c>
-      <c r="B2" s="11" t="s">
+      <c r="B2" s="12" t="s">
         <v>46</v>
       </c>
-      <c r="C2" s="12" t="s">
+      <c r="C2" s="13" t="s">
         <v>47</v>
       </c>
-      <c r="D2" s="11" t="s">
+      <c r="D2" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="E2" s="12" t="s">
+      <c r="E2" s="13" t="s">
         <v>49</v>
       </c>
-      <c r="F2" s="12" t="s">
+      <c r="F2" s="13" t="s">
         <v>50</v>
       </c>
-      <c r="G2" s="23" t="s">
+      <c r="G2" s="24" t="s">
         <v>51</v>
       </c>
-      <c r="H2" s="12" t="s">
+      <c r="H2" s="13" t="s">
         <v>52</v>
       </c>
-      <c r="I2" s="12">
+      <c r="I2" s="13">
         <v>5</v>
       </c>
-      <c r="J2" s="12" t="s">
+      <c r="J2" s="13" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="3" ht="108" customHeight="1" spans="1:10">
-      <c r="A3" s="11">
+      <c r="A3" s="12">
         <v>2</v>
       </c>
-      <c r="B3" s="11" t="s">
+      <c r="B3" s="12" t="s">
         <v>54</v>
       </c>
-      <c r="C3" s="12" t="s">
+      <c r="C3" s="13" t="s">
         <v>55</v>
       </c>
-      <c r="D3" s="11" t="s">
+      <c r="D3" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="E3" s="12" t="s">
+      <c r="E3" s="13" t="s">
         <v>56</v>
       </c>
-      <c r="F3" s="12" t="s">
+      <c r="F3" s="13" t="s">
         <v>57</v>
       </c>
-      <c r="G3" s="23" t="s">
+      <c r="G3" s="24" t="s">
         <v>58</v>
       </c>
-      <c r="H3" s="12" t="s">
+      <c r="H3" s="13" t="s">
         <v>59</v>
       </c>
-      <c r="I3" s="11">
+      <c r="I3" s="12">
         <v>4</v>
       </c>
-      <c r="J3" s="12" t="s">
+      <c r="J3" s="13" t="s">
         <v>60</v>
       </c>
     </row>
     <row r="4" ht="115.2" spans="1:10">
-      <c r="A4" s="11">
+      <c r="A4" s="12">
         <v>3</v>
       </c>
-      <c r="B4" s="11" t="s">
+      <c r="B4" s="12" t="s">
         <v>61</v>
       </c>
-      <c r="C4" s="12" t="s">
+      <c r="C4" s="13" t="s">
         <v>62</v>
       </c>
-      <c r="D4" s="11" t="s">
+      <c r="D4" s="12" t="s">
         <v>63</v>
       </c>
-      <c r="E4" s="12" t="s">
+      <c r="E4" s="13" t="s">
         <v>64</v>
       </c>
-      <c r="F4" s="12" t="s">
+      <c r="F4" s="13" t="s">
         <v>65</v>
       </c>
-      <c r="G4" s="14" t="s">
+      <c r="G4" s="15" t="s">
         <v>66</v>
       </c>
-      <c r="H4" s="12" t="s">
+      <c r="H4" s="13" t="s">
         <v>67</v>
       </c>
-      <c r="I4" s="11">
+      <c r="I4" s="12">
         <v>4</v>
       </c>
-      <c r="J4" s="12" t="s">
+      <c r="J4" s="13" t="s">
         <v>68</v>
       </c>
     </row>
@@ -2462,162 +2466,162 @@
       </c>
     </row>
     <row r="2" ht="121.05" customHeight="1" spans="1:10">
-      <c r="A2" s="11">
+      <c r="A2" s="12">
         <v>1</v>
       </c>
-      <c r="B2" s="11" t="s">
+      <c r="B2" s="12" t="s">
         <v>61</v>
       </c>
-      <c r="C2" s="12" t="s">
+      <c r="C2" s="13" t="s">
         <v>69</v>
       </c>
-      <c r="D2" s="12" t="s">
+      <c r="D2" s="13" t="s">
         <v>48</v>
       </c>
-      <c r="E2" s="13" t="s">
+      <c r="E2" s="14" t="s">
         <v>70</v>
       </c>
-      <c r="F2" s="12" t="s">
+      <c r="F2" s="13" t="s">
         <v>71</v>
       </c>
-      <c r="G2" s="14" t="s">
+      <c r="G2" s="15" t="s">
         <v>72</v>
       </c>
-      <c r="H2" s="12" t="s">
+      <c r="H2" s="13" t="s">
         <v>73</v>
       </c>
-      <c r="I2" s="12">
+      <c r="I2" s="13">
         <v>5</v>
       </c>
-      <c r="J2" s="12" t="s">
+      <c r="J2" s="13" t="s">
         <v>74</v>
       </c>
     </row>
     <row r="3" ht="142.95" customHeight="1" spans="1:10">
-      <c r="A3" s="11">
+      <c r="A3" s="12">
         <v>2</v>
       </c>
-      <c r="B3" s="15" t="s">
+      <c r="B3" s="16" t="s">
         <v>75</v>
       </c>
-      <c r="C3" s="15" t="s">
+      <c r="C3" s="16" t="s">
         <v>76</v>
       </c>
-      <c r="D3" s="15" t="s">
+      <c r="D3" s="16" t="s">
         <v>77</v>
       </c>
-      <c r="E3" s="15" t="s">
+      <c r="E3" s="16" t="s">
         <v>78</v>
       </c>
-      <c r="F3" s="15" t="s">
+      <c r="F3" s="16" t="s">
         <v>79</v>
       </c>
-      <c r="G3" s="14" t="s">
+      <c r="G3" s="15" t="s">
         <v>80</v>
       </c>
-      <c r="H3" s="12" t="s">
+      <c r="H3" s="13" t="s">
         <v>81</v>
       </c>
-      <c r="I3" s="11">
+      <c r="I3" s="12">
         <v>5</v>
       </c>
-      <c r="J3" s="12" t="s">
+      <c r="J3" s="13" t="s">
         <v>82</v>
       </c>
     </row>
     <row r="4" ht="139.05" customHeight="1" spans="1:10">
-      <c r="A4" s="11">
+      <c r="A4" s="12">
         <v>3</v>
       </c>
-      <c r="B4" s="11" t="s">
+      <c r="B4" s="12" t="s">
         <v>46</v>
       </c>
-      <c r="C4" s="12" t="s">
+      <c r="C4" s="13" t="s">
         <v>83</v>
       </c>
-      <c r="D4" s="16" t="s">
+      <c r="D4" s="17" t="s">
         <v>84</v>
       </c>
-      <c r="E4" s="12" t="s">
+      <c r="E4" s="13" t="s">
         <v>85</v>
       </c>
-      <c r="F4" s="12" t="s">
+      <c r="F4" s="13" t="s">
         <v>86</v>
       </c>
-      <c r="G4" s="14" t="s">
+      <c r="G4" s="15" t="s">
         <v>87</v>
       </c>
-      <c r="H4" s="12" t="s">
+      <c r="H4" s="13" t="s">
         <v>88</v>
       </c>
-      <c r="I4" s="11">
+      <c r="I4" s="12">
         <v>4</v>
       </c>
-      <c r="J4" s="12" t="s">
+      <c r="J4" s="13" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="5" ht="187.2" spans="1:10">
-      <c r="A5" s="11">
+      <c r="A5" s="12">
         <v>4</v>
       </c>
-      <c r="B5" s="17" t="s">
+      <c r="B5" s="18" t="s">
         <v>61</v>
       </c>
-      <c r="C5" s="17" t="s">
+      <c r="C5" s="18" t="s">
         <v>90</v>
       </c>
-      <c r="D5" s="18" t="s">
+      <c r="D5" s="19" t="s">
         <v>63</v>
       </c>
-      <c r="E5" s="17" t="s">
+      <c r="E5" s="18" t="s">
         <v>91</v>
       </c>
-      <c r="F5" s="17" t="s">
+      <c r="F5" s="18" t="s">
         <v>92</v>
       </c>
-      <c r="G5" s="19" t="s">
+      <c r="G5" s="20" t="s">
         <v>93</v>
       </c>
-      <c r="H5" s="17" t="s">
+      <c r="H5" s="18" t="s">
         <v>94</v>
       </c>
-      <c r="I5" s="12">
+      <c r="I5" s="13">
         <v>4</v>
       </c>
-      <c r="J5" s="17" t="s">
+      <c r="J5" s="18" t="s">
         <v>95</v>
       </c>
     </row>
     <row r="6" ht="144" spans="1:10">
-      <c r="A6" s="11">
+      <c r="A6" s="12">
         <v>5</v>
       </c>
-      <c r="B6" s="13" t="s">
+      <c r="B6" s="14" t="s">
         <v>46</v>
       </c>
-      <c r="C6" s="13" t="s">
+      <c r="C6" s="14" t="s">
         <v>96</v>
       </c>
-      <c r="D6" s="20" t="s">
+      <c r="D6" s="21" t="s">
         <v>84</v>
       </c>
-      <c r="E6" s="12" t="s">
+      <c r="E6" s="13" t="s">
         <v>97</v>
       </c>
-      <c r="F6" s="21" t="s">
+      <c r="F6" s="22" t="s">
         <v>98</v>
       </c>
-      <c r="G6" s="22" t="s">
+      <c r="G6" s="23" t="s">
         <v>99</v>
       </c>
-      <c r="H6" s="13" t="s">
+      <c r="H6" s="14" t="s">
         <v>100</v>
       </c>
-      <c r="I6" s="12">
+      <c r="I6" s="13">
         <v>5</v>
       </c>
-      <c r="J6" s="13" t="s">
+      <c r="J6" s="14" t="s">
         <v>101</v>
       </c>
     </row>
@@ -2703,7 +2707,7 @@
       <c r="F2" s="8" t="s">
         <v>105</v>
       </c>
-      <c r="G2" s="9" t="s">
+      <c r="G2" s="11" t="s">
         <v>106</v>
       </c>
       <c r="H2" s="8" t="s">
@@ -2735,7 +2739,7 @@
       <c r="F3" s="8" t="s">
         <v>112</v>
       </c>
-      <c r="G3" s="9" t="s">
+      <c r="G3" s="11" t="s">
         <v>113</v>
       </c>
       <c r="H3" s="8" t="s">
@@ -2767,7 +2771,7 @@
       <c r="F4" s="8" t="s">
         <v>119</v>
       </c>
-      <c r="G4" s="9" t="s">
+      <c r="G4" s="11" t="s">
         <v>120</v>
       </c>
       <c r="H4" s="8" t="s">
@@ -2799,7 +2803,7 @@
       <c r="F5" s="8" t="s">
         <v>125</v>
       </c>
-      <c r="G5" s="9" t="s">
+      <c r="G5" s="11" t="s">
         <v>126</v>
       </c>
       <c r="H5" s="8" t="s">
@@ -2831,7 +2835,7 @@
       <c r="F6" s="8" t="s">
         <v>132</v>
       </c>
-      <c r="G6" s="9" t="s">
+      <c r="G6" s="11" t="s">
         <v>133</v>
       </c>
       <c r="H6" s="8" t="s">
@@ -2860,6 +2864,132 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
+  <dimension ref="A1:J6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="5"/>
+  <cols>
+    <col min="1" max="1" width="5" customWidth="1"/>
+    <col min="2" max="2" width="14" customWidth="1"/>
+    <col min="3" max="3" width="30" customWidth="1"/>
+    <col min="4" max="4" width="14" customWidth="1"/>
+    <col min="5" max="5" width="26" customWidth="1"/>
+    <col min="6" max="6" width="30" customWidth="1"/>
+    <col min="7" max="7" width="18" customWidth="1"/>
+    <col min="8" max="8" width="20" customWidth="1"/>
+    <col min="9" max="9" width="10" customWidth="1"/>
+    <col min="10" max="10" width="26" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="30" customHeight="1" spans="1:10">
+      <c r="A1" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="D1" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="E1" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="F1" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="G1" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="H1" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="I1" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="J1" s="5" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10">
+      <c r="A2" s="6">
+        <v>1</v>
+      </c>
+      <c r="B2" s="7"/>
+      <c r="C2" s="8"/>
+      <c r="D2" s="8"/>
+      <c r="E2" s="8"/>
+      <c r="F2" s="8"/>
+      <c r="G2" s="9"/>
+      <c r="H2" s="8"/>
+      <c r="I2" s="8"/>
+      <c r="J2" s="8"/>
+    </row>
+    <row r="3" spans="1:10">
+      <c r="A3" s="10">
+        <v>2</v>
+      </c>
+      <c r="B3" s="8"/>
+      <c r="C3" s="8"/>
+      <c r="D3" s="8"/>
+      <c r="E3" s="8"/>
+      <c r="F3" s="8"/>
+      <c r="G3" s="9"/>
+      <c r="H3" s="8"/>
+      <c r="I3" s="8"/>
+      <c r="J3" s="8"/>
+    </row>
+    <row r="4" spans="1:10">
+      <c r="A4" s="10">
+        <v>3</v>
+      </c>
+      <c r="B4" s="8"/>
+      <c r="C4" s="8"/>
+      <c r="D4" s="8"/>
+      <c r="E4" s="8"/>
+      <c r="F4" s="8"/>
+      <c r="G4" s="9"/>
+      <c r="H4" s="8"/>
+      <c r="I4" s="8"/>
+      <c r="J4" s="8"/>
+    </row>
+    <row r="5" spans="1:10">
+      <c r="A5" s="10">
+        <v>4</v>
+      </c>
+      <c r="B5" s="8"/>
+      <c r="C5" s="8"/>
+      <c r="D5" s="8"/>
+      <c r="E5" s="8"/>
+      <c r="F5" s="8"/>
+      <c r="G5" s="9"/>
+      <c r="H5" s="8"/>
+      <c r="I5" s="8"/>
+      <c r="J5" s="8"/>
+    </row>
+    <row r="6" spans="1:10">
+      <c r="A6" s="10">
+        <v>5</v>
+      </c>
+      <c r="B6" s="8"/>
+      <c r="C6" s="8"/>
+      <c r="D6" s="8"/>
+      <c r="E6" s="8"/>
+      <c r="F6" s="8"/>
+      <c r="G6" s="9"/>
+      <c r="H6" s="8"/>
+      <c r="I6" s="8"/>
+      <c r="J6" s="8"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:B11"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="1"/>
   <cols>

--- a/docs/PRJ301_SE20C_GROUP4.xlsx
+++ b/docs/PRJ301_SE20C_GROUP4.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="206" uniqueCount="148">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="214" uniqueCount="156">
   <si>
     <t>PRJ301 - Project AI Usage Report</t>
   </si>
@@ -850,6 +850,31 @@
   </si>
   <si>
     <t>AI's error messages were in English; manually translated them to Vietnamese to match the system's language requirement.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Implementation &amp; Security
+</t>
+  </si>
+  <si>
+    <t>Implement Session management (HttpSession) and Cookie state for Remember Me functionality</t>
+  </si>
+  <si>
+    <t>Chatgpt,codex</t>
+  </si>
+  <si>
+    <t>Generated code for managing user login sessions with HttpSession, storing currentUser and role, and implementing a 7-day persistent Cookie for the 'Remember Me' feature in AuthController.</t>
+  </si>
+  <si>
+    <t>Integrated HttpSession with AuthFilter for route protection (/user, /add, /update, /delete). Customized Cookie maxAge (7 days when checked, 0 to clear when unchecked) and configured proper redirect to login page upon invalid/expired session.</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/drive/folders/1uyrqO7T6EU5SHkkqS9n9vUqZ1ghX6fXp?usp=sharing</t>
+  </si>
+  <si>
+    <t>1 Controller (AuthController) handling Session/Cookie, 2 Cookies configured (cuser, cpass), 1 Filter (AuthFilter) checking session state</t>
+  </si>
+  <si>
+    <t>AI forgot to handle clearing the cookie when 'Remember Me' was unchecked, leaving stale data in the browser; manually implemented cookie deletion (setMaxAge(0)) and added session timeout handling.</t>
   </si>
   <si>
     <t>Column</t>
@@ -941,7 +966,7 @@
     <font>
       <u/>
       <sz val="11"/>
-      <color rgb="FF800080"/>
+      <color rgb="FF0000FF"/>
       <name val="Calibri"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -955,7 +980,7 @@
     <font>
       <u/>
       <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <color rgb="FF800080"/>
       <name val="Calibri"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -1498,7 +1523,7 @@
     <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1654,13 +1679,13 @@
     <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="6" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="6" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -1672,7 +1697,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="6" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="6" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1687,7 +1712,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="6" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="6" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -1696,10 +1721,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="6" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="6" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="6" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="6" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2707,7 +2732,7 @@
       <c r="F2" s="8" t="s">
         <v>105</v>
       </c>
-      <c r="G2" s="11" t="s">
+      <c r="G2" s="9" t="s">
         <v>106</v>
       </c>
       <c r="H2" s="8" t="s">
@@ -2739,7 +2764,7 @@
       <c r="F3" s="8" t="s">
         <v>112</v>
       </c>
-      <c r="G3" s="11" t="s">
+      <c r="G3" s="9" t="s">
         <v>113</v>
       </c>
       <c r="H3" s="8" t="s">
@@ -2771,7 +2796,7 @@
       <c r="F4" s="8" t="s">
         <v>119</v>
       </c>
-      <c r="G4" s="11" t="s">
+      <c r="G4" s="9" t="s">
         <v>120</v>
       </c>
       <c r="H4" s="8" t="s">
@@ -2803,7 +2828,7 @@
       <c r="F5" s="8" t="s">
         <v>125</v>
       </c>
-      <c r="G5" s="11" t="s">
+      <c r="G5" s="9" t="s">
         <v>126</v>
       </c>
       <c r="H5" s="8" t="s">
@@ -2835,7 +2860,7 @@
       <c r="F6" s="8" t="s">
         <v>132</v>
       </c>
-      <c r="G6" s="11" t="s">
+      <c r="G6" s="9" t="s">
         <v>133</v>
       </c>
       <c r="H6" s="8" t="s">
@@ -2911,19 +2936,37 @@
         <v>45</v>
       </c>
     </row>
-    <row r="2" spans="1:10">
+    <row r="2" ht="110.4" spans="1:10">
       <c r="A2" s="6">
         <v>1</v>
       </c>
-      <c r="B2" s="7"/>
-      <c r="C2" s="8"/>
-      <c r="D2" s="8"/>
-      <c r="E2" s="8"/>
-      <c r="F2" s="8"/>
-      <c r="G2" s="9"/>
-      <c r="H2" s="8"/>
-      <c r="I2" s="8"/>
-      <c r="J2" s="8"/>
+      <c r="B2" s="7" t="s">
+        <v>136</v>
+      </c>
+      <c r="C2" s="8" t="s">
+        <v>137</v>
+      </c>
+      <c r="D2" s="8" t="s">
+        <v>138</v>
+      </c>
+      <c r="E2" s="8" t="s">
+        <v>139</v>
+      </c>
+      <c r="F2" s="8" t="s">
+        <v>140</v>
+      </c>
+      <c r="G2" s="9" t="s">
+        <v>141</v>
+      </c>
+      <c r="H2" s="8" t="s">
+        <v>142</v>
+      </c>
+      <c r="I2" s="8">
+        <v>5</v>
+      </c>
+      <c r="J2" s="8" t="s">
+        <v>143</v>
+      </c>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" s="10">
@@ -2934,7 +2977,7 @@
       <c r="D3" s="8"/>
       <c r="E3" s="8"/>
       <c r="F3" s="8"/>
-      <c r="G3" s="9"/>
+      <c r="G3" s="11"/>
       <c r="H3" s="8"/>
       <c r="I3" s="8"/>
       <c r="J3" s="8"/>
@@ -2948,7 +2991,7 @@
       <c r="D4" s="8"/>
       <c r="E4" s="8"/>
       <c r="F4" s="8"/>
-      <c r="G4" s="9"/>
+      <c r="G4" s="11"/>
       <c r="H4" s="8"/>
       <c r="I4" s="8"/>
       <c r="J4" s="8"/>
@@ -2962,7 +3005,7 @@
       <c r="D5" s="8"/>
       <c r="E5" s="8"/>
       <c r="F5" s="8"/>
-      <c r="G5" s="9"/>
+      <c r="G5" s="11"/>
       <c r="H5" s="8"/>
       <c r="I5" s="8"/>
       <c r="J5" s="8"/>
@@ -2976,12 +3019,15 @@
       <c r="D6" s="8"/>
       <c r="E6" s="8"/>
       <c r="F6" s="8"/>
-      <c r="G6" s="9"/>
+      <c r="G6" s="11"/>
       <c r="H6" s="8"/>
       <c r="I6" s="8"/>
       <c r="J6" s="8"/>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="G2" r:id="rId1" display="https://drive.google.com/drive/folders/1uyrqO7T6EU5SHkkqS9n9vUqZ1ghX6fXp?usp=sharing"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
 </worksheet>
@@ -2999,10 +3045,10 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
-        <v>136</v>
+        <v>144</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>137</v>
+        <v>145</v>
       </c>
     </row>
     <row r="2" spans="1:2">
@@ -3010,7 +3056,7 @@
         <v>36</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>138</v>
+        <v>146</v>
       </c>
     </row>
     <row r="3" ht="26.4" spans="1:2">
@@ -3018,7 +3064,7 @@
         <v>37</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>139</v>
+        <v>147</v>
       </c>
     </row>
     <row r="4" ht="26.4" spans="1:2">
@@ -3026,7 +3072,7 @@
         <v>38</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>140</v>
+        <v>148</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -3034,7 +3080,7 @@
         <v>39</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>141</v>
+        <v>149</v>
       </c>
     </row>
     <row r="6" ht="26.4" spans="1:2">
@@ -3042,7 +3088,7 @@
         <v>40</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>142</v>
+        <v>150</v>
       </c>
     </row>
     <row r="7" ht="26.4" spans="1:2">
@@ -3050,7 +3096,7 @@
         <v>41</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>143</v>
+        <v>151</v>
       </c>
     </row>
     <row r="8" ht="39.6" spans="1:2">
@@ -3058,7 +3104,7 @@
         <v>42</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>144</v>
+        <v>152</v>
       </c>
     </row>
     <row r="9" ht="26.4" spans="1:2">
@@ -3066,7 +3112,7 @@
         <v>43</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>145</v>
+        <v>153</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -3074,7 +3120,7 @@
         <v>44</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>146</v>
+        <v>154</v>
       </c>
     </row>
     <row r="11" ht="26.4" spans="1:2">
@@ -3082,7 +3128,7 @@
         <v>45</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>147</v>
+        <v>155</v>
       </c>
     </row>
   </sheetData>
